--- a/data/trans_orig/P43D-Clase-trans_orig.xlsx
+++ b/data/trans_orig/P43D-Clase-trans_orig.xlsx
@@ -673,12 +673,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>21424</t>
+          <t>22012</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>41788</t>
+          <t>41492</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -688,12 +688,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>9,68%</t>
+          <t>9,94%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>18,88%</t>
+          <t>18,74%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -708,12 +708,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>21424</t>
+          <t>22012</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>41788</t>
+          <t>41492</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -723,12 +723,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>9,68%</t>
+          <t>9,94%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>18,88%</t>
+          <t>18,74%</t>
         </is>
       </c>
     </row>
@@ -751,12 +751,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>61050</t>
+          <t>59492</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>88190</t>
+          <t>87676</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -766,12 +766,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>27,58%</t>
+          <t>26,87%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>39,84%</t>
+          <t>39,6%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -786,12 +786,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>61050</t>
+          <t>59492</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>88190</t>
+          <t>87676</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -801,12 +801,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>27,58%</t>
+          <t>26,87%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>39,84%</t>
+          <t>39,6%</t>
         </is>
       </c>
     </row>
@@ -829,12 +829,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>58431</t>
+          <t>58526</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>85628</t>
+          <t>85475</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -844,12 +844,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>26,39%</t>
+          <t>26,44%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>38,68%</t>
+          <t>38,61%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -864,12 +864,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>58431</t>
+          <t>58526</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>85628</t>
+          <t>85475</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -879,12 +879,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>26,39%</t>
+          <t>26,44%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>38,68%</t>
+          <t>38,61%</t>
         </is>
       </c>
     </row>
@@ -907,12 +907,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>33590</t>
+          <t>33467</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>56638</t>
+          <t>56998</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -922,12 +922,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>15,17%</t>
+          <t>15,12%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>25,58%</t>
+          <t>25,75%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -942,12 +942,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>33590</t>
+          <t>33467</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>56638</t>
+          <t>56998</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -957,12 +957,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>15,17%</t>
+          <t>15,12%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>25,58%</t>
+          <t>25,75%</t>
         </is>
       </c>
     </row>
@@ -1067,12 +1067,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>25624</t>
+          <t>26699</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>47954</t>
+          <t>48839</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -1082,12 +1082,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>10,34%</t>
+          <t>10,78%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>19,36%</t>
+          <t>19,71%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -1102,12 +1102,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>25624</t>
+          <t>26699</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>47954</t>
+          <t>48839</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1117,12 +1117,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>10,34%</t>
+          <t>10,78%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>19,36%</t>
+          <t>19,71%</t>
         </is>
       </c>
     </row>
@@ -1145,12 +1145,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>57232</t>
+          <t>56461</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>85644</t>
+          <t>85194</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1160,12 +1160,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>23,1%</t>
+          <t>22,79%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>34,57%</t>
+          <t>34,39%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1180,12 +1180,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>57232</t>
+          <t>56461</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>85644</t>
+          <t>85194</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1195,12 +1195,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>23,1%</t>
+          <t>22,79%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>34,57%</t>
+          <t>34,39%</t>
         </is>
       </c>
     </row>
@@ -1223,12 +1223,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>61181</t>
+          <t>60010</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>89537</t>
+          <t>88485</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1238,12 +1238,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>24,69%</t>
+          <t>24,22%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>36,14%</t>
+          <t>35,71%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1258,12 +1258,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>61181</t>
+          <t>60010</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>89537</t>
+          <t>88485</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1273,12 +1273,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>24,69%</t>
+          <t>24,22%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>36,14%</t>
+          <t>35,71%</t>
         </is>
       </c>
     </row>
@@ -1301,12 +1301,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>53692</t>
+          <t>55110</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>82591</t>
+          <t>82690</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1316,12 +1316,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>21,67%</t>
+          <t>22,24%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>33,34%</t>
+          <t>33,38%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1336,12 +1336,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>53692</t>
+          <t>55110</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>82591</t>
+          <t>82690</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1351,12 +1351,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>21,67%</t>
+          <t>22,24%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>33,34%</t>
+          <t>33,38%</t>
         </is>
       </c>
     </row>
@@ -1461,12 +1461,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>13920</t>
+          <t>13503</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>30150</t>
+          <t>31114</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1476,12 +1476,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>12,85%</t>
+          <t>12,46%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>27,83%</t>
+          <t>28,72%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1496,12 +1496,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>13920</t>
+          <t>13503</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>30150</t>
+          <t>31114</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1511,12 +1511,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>12,85%</t>
+          <t>12,46%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>27,83%</t>
+          <t>28,72%</t>
         </is>
       </c>
     </row>
@@ -1539,12 +1539,12 @@
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>24048</t>
+          <t>24236</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>43361</t>
+          <t>43966</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -1554,12 +1554,12 @@
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>22,2%</t>
+          <t>22,37%</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>40,02%</t>
+          <t>40,58%</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -1574,12 +1574,12 @@
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>24048</t>
+          <t>24236</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>43361</t>
+          <t>43966</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -1589,12 +1589,12 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>22,2%</t>
+          <t>22,37%</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>40,02%</t>
+          <t>40,58%</t>
         </is>
       </c>
     </row>
@@ -1617,12 +1617,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>23228</t>
+          <t>23554</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>42357</t>
+          <t>43678</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -1632,12 +1632,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>21,44%</t>
+          <t>21,74%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>39,1%</t>
+          <t>40,32%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -1652,12 +1652,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>23228</t>
+          <t>23554</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>42357</t>
+          <t>43678</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -1667,12 +1667,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>21,44%</t>
+          <t>21,74%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>39,1%</t>
+          <t>40,32%</t>
         </is>
       </c>
     </row>
@@ -1695,12 +1695,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>13480</t>
+          <t>13505</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>29441</t>
+          <t>30234</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -1710,12 +1710,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>12,44%</t>
+          <t>12,47%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>27,17%</t>
+          <t>27,91%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -1730,12 +1730,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>13480</t>
+          <t>13505</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>29441</t>
+          <t>30234</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -1745,12 +1745,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>12,44%</t>
+          <t>12,47%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>27,17%</t>
+          <t>27,91%</t>
         </is>
       </c>
     </row>
@@ -1855,12 +1855,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>71072</t>
+          <t>70755</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>103356</t>
+          <t>104437</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -1870,12 +1870,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>17,94%</t>
+          <t>17,86%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>26,1%</t>
+          <t>26,37%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -1890,12 +1890,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>71072</t>
+          <t>70755</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>103356</t>
+          <t>104437</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -1905,12 +1905,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>17,94%</t>
+          <t>17,86%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>26,1%</t>
+          <t>26,37%</t>
         </is>
       </c>
     </row>
@@ -1933,12 +1933,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>120566</t>
+          <t>120672</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>159440</t>
+          <t>158204</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -1948,12 +1948,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>30,44%</t>
+          <t>30,47%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>40,26%</t>
+          <t>39,94%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -1968,12 +1968,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>120566</t>
+          <t>120672</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>159440</t>
+          <t>158204</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -1983,12 +1983,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>30,44%</t>
+          <t>30,47%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>40,26%</t>
+          <t>39,94%</t>
         </is>
       </c>
     </row>
@@ -2011,12 +2011,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>93825</t>
+          <t>94233</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>128776</t>
+          <t>129251</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -2026,12 +2026,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>23,69%</t>
+          <t>23,79%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>32,51%</t>
+          <t>32,63%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -2046,12 +2046,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>93825</t>
+          <t>94233</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>128776</t>
+          <t>129251</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -2061,12 +2061,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>23,69%</t>
+          <t>23,79%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>32,51%</t>
+          <t>32,63%</t>
         </is>
       </c>
     </row>
@@ -2089,12 +2089,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>45632</t>
+          <t>45707</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>74661</t>
+          <t>73843</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2104,12 +2104,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>11,52%</t>
+          <t>11,54%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>18,85%</t>
+          <t>18,64%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2124,12 +2124,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>45632</t>
+          <t>45707</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>74661</t>
+          <t>73843</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2139,12 +2139,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>11,52%</t>
+          <t>11,54%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>18,85%</t>
+          <t>18,64%</t>
         </is>
       </c>
     </row>
@@ -2249,12 +2249,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>55084</t>
+          <t>55942</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>83920</t>
+          <t>86330</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -2264,12 +2264,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>17,71%</t>
+          <t>17,98%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>26,97%</t>
+          <t>27,75%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -2284,12 +2284,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>55084</t>
+          <t>55942</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>83920</t>
+          <t>86330</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -2299,12 +2299,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>17,71%</t>
+          <t>17,98%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>26,97%</t>
+          <t>27,75%</t>
         </is>
       </c>
     </row>
@@ -2327,12 +2327,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>92779</t>
+          <t>93396</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>127155</t>
+          <t>126417</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -2342,12 +2342,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>29,82%</t>
+          <t>30,02%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>40,87%</t>
+          <t>40,63%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -2362,12 +2362,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>92779</t>
+          <t>93396</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>127155</t>
+          <t>126417</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -2377,12 +2377,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>29,82%</t>
+          <t>30,02%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>40,87%</t>
+          <t>40,63%</t>
         </is>
       </c>
     </row>
@@ -2405,12 +2405,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>61038</t>
+          <t>61186</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>92822</t>
+          <t>92467</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -2420,12 +2420,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>19,62%</t>
+          <t>19,67%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>29,84%</t>
+          <t>29,72%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -2440,12 +2440,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>61038</t>
+          <t>61186</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>92822</t>
+          <t>92467</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -2455,12 +2455,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>19,62%</t>
+          <t>19,67%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>29,84%</t>
+          <t>29,72%</t>
         </is>
       </c>
     </row>
@@ -2483,12 +2483,12 @@
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>43034</t>
+          <t>43248</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>70837</t>
+          <t>71218</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
@@ -2498,12 +2498,12 @@
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>13,83%</t>
+          <t>13,9%</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>22,77%</t>
+          <t>22,89%</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
@@ -2518,12 +2518,12 @@
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>43034</t>
+          <t>43248</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>70837</t>
+          <t>71218</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -2533,12 +2533,12 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>13,83%</t>
+          <t>13,9%</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
         <is>
-          <t>22,77%</t>
+          <t>22,89%</t>
         </is>
       </c>
     </row>
@@ -2623,7 +2623,7 @@
     <row r="29">
       <c r="A29" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>No ha trabajado</t>
         </is>
       </c>
       <c r="B29" s="3" t="inlineStr">
@@ -2643,12 +2643,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>153910</t>
+          <t>154721</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>196514</t>
+          <t>197645</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -2658,12 +2658,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>31,2%</t>
+          <t>31,36%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>39,83%</t>
+          <t>40,06%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -2678,12 +2678,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>153910</t>
+          <t>154721</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>196514</t>
+          <t>197645</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -2693,12 +2693,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>31,2%</t>
+          <t>31,36%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>39,83%</t>
+          <t>40,06%</t>
         </is>
       </c>
     </row>
@@ -2721,12 +2721,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>109950</t>
+          <t>108494</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>149605</t>
+          <t>147975</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -2736,12 +2736,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>22,29%</t>
+          <t>21,99%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>30,32%</t>
+          <t>29,99%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -2756,12 +2756,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>109950</t>
+          <t>108494</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>149605</t>
+          <t>147975</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -2771,12 +2771,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>22,29%</t>
+          <t>21,99%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>30,32%</t>
+          <t>29,99%</t>
         </is>
       </c>
     </row>
@@ -2799,12 +2799,12 @@
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>87676</t>
+          <t>89011</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>123465</t>
+          <t>124476</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -2814,12 +2814,12 @@
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>17,77%</t>
+          <t>18,04%</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>25,02%</t>
+          <t>25,23%</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
@@ -2834,12 +2834,12 @@
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>87676</t>
+          <t>89011</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>123465</t>
+          <t>124476</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
@@ -2849,12 +2849,12 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>17,77%</t>
+          <t>18,04%</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>25,02%</t>
+          <t>25,23%</t>
         </is>
       </c>
     </row>
@@ -2877,12 +2877,12 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>67514</t>
+          <t>67569</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>100442</t>
+          <t>99912</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -2892,12 +2892,12 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>13,68%</t>
+          <t>13,7%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>20,36%</t>
+          <t>20,25%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -2912,12 +2912,12 @@
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>67514</t>
+          <t>67569</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>100442</t>
+          <t>99912</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -2927,12 +2927,12 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>13,68%</t>
+          <t>13,7%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>20,36%</t>
+          <t>20,25%</t>
         </is>
       </c>
     </row>
@@ -3037,12 +3037,12 @@
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>386749</t>
+          <t>386005</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>456653</t>
+          <t>460230</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
@@ -3052,12 +3052,12 @@
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>21,75%</t>
+          <t>21,71%</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>25,68%</t>
+          <t>25,88%</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
@@ -3072,12 +3072,12 @@
       </c>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t>386749</t>
+          <t>386005</t>
         </is>
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>456653</t>
+          <t>460230</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
@@ -3087,12 +3087,12 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>21,75%</t>
+          <t>21,71%</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>25,68%</t>
+          <t>25,88%</t>
         </is>
       </c>
     </row>
@@ -3115,12 +3115,12 @@
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>510249</t>
+          <t>516626</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>593059</t>
+          <t>591593</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
@@ -3130,12 +3130,12 @@
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>28,7%</t>
+          <t>29,06%</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>33,35%</t>
+          <t>33,27%</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
@@ -3150,12 +3150,12 @@
       </c>
       <c r="L35" s="2" t="inlineStr">
         <is>
-          <t>510249</t>
+          <t>516626</t>
         </is>
       </c>
       <c r="M35" s="2" t="inlineStr">
         <is>
-          <t>593059</t>
+          <t>591593</t>
         </is>
       </c>
       <c r="N35" s="2" t="inlineStr">
@@ -3165,12 +3165,12 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>28,7%</t>
+          <t>29,06%</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
         <is>
-          <t>33,35%</t>
+          <t>33,27%</t>
         </is>
       </c>
     </row>
@@ -3193,12 +3193,12 @@
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>436532</t>
+          <t>436264</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>511423</t>
+          <t>510375</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
@@ -3208,12 +3208,12 @@
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>24,55%</t>
+          <t>24,54%</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>28,76%</t>
+          <t>28,7%</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr">
@@ -3228,12 +3228,12 @@
       </c>
       <c r="L36" s="2" t="inlineStr">
         <is>
-          <t>436532</t>
+          <t>436264</t>
         </is>
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>511423</t>
+          <t>510375</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
@@ -3243,12 +3243,12 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>24,55%</t>
+          <t>24,54%</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t>28,76%</t>
+          <t>28,7%</t>
         </is>
       </c>
     </row>
@@ -3271,12 +3271,12 @@
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>297473</t>
+          <t>297600</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>366737</t>
+          <t>361943</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
@@ -3286,12 +3286,12 @@
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>16,73%</t>
+          <t>16,74%</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>20,63%</t>
+          <t>20,36%</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
@@ -3306,12 +3306,12 @@
       </c>
       <c r="L37" s="2" t="inlineStr">
         <is>
-          <t>297473</t>
+          <t>297600</t>
         </is>
       </c>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t>366737</t>
+          <t>361943</t>
         </is>
       </c>
       <c r="N37" s="2" t="inlineStr">
@@ -3321,12 +3321,12 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>16,73%</t>
+          <t>16,74%</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
         <is>
-          <t>20,63%</t>
+          <t>20,36%</t>
         </is>
       </c>
     </row>
@@ -3604,12 +3604,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>19784</t>
+          <t>19585</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>42715</t>
+          <t>42364</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -3619,12 +3619,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>7,73%</t>
+          <t>7,65%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>16,69%</t>
+          <t>16,55%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -3639,12 +3639,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>19784</t>
+          <t>19585</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>42715</t>
+          <t>42364</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -3654,12 +3654,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>7,73%</t>
+          <t>7,65%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>16,69%</t>
+          <t>16,55%</t>
         </is>
       </c>
     </row>
@@ -3682,12 +3682,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>62669</t>
+          <t>63755</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>94558</t>
+          <t>94834</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -3697,12 +3697,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>24,49%</t>
+          <t>24,91%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>36,95%</t>
+          <t>37,06%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -3717,12 +3717,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>62669</t>
+          <t>63755</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>94558</t>
+          <t>94834</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -3732,12 +3732,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>24,49%</t>
+          <t>24,91%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>36,95%</t>
+          <t>37,06%</t>
         </is>
       </c>
     </row>
@@ -3760,12 +3760,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>81563</t>
+          <t>81583</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>114494</t>
+          <t>113787</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -3775,12 +3775,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>31,87%</t>
+          <t>31,88%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>44,74%</t>
+          <t>44,46%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -3795,12 +3795,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>81563</t>
+          <t>81583</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>114494</t>
+          <t>113787</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -3810,12 +3810,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>31,87%</t>
+          <t>31,88%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>44,74%</t>
+          <t>44,46%</t>
         </is>
       </c>
     </row>
@@ -3838,12 +3838,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>37333</t>
+          <t>40297</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>66183</t>
+          <t>67257</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -3853,12 +3853,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>14,59%</t>
+          <t>15,75%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>25,86%</t>
+          <t>26,28%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -3873,12 +3873,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>37333</t>
+          <t>40297</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>66183</t>
+          <t>67257</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -3888,12 +3888,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>14,59%</t>
+          <t>15,75%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>25,86%</t>
+          <t>26,28%</t>
         </is>
       </c>
     </row>
@@ -3998,12 +3998,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>24899</t>
+          <t>24378</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>46432</t>
+          <t>46663</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -4013,12 +4013,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>9,19%</t>
+          <t>9,0%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>17,14%</t>
+          <t>17,22%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -4033,12 +4033,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>24899</t>
+          <t>24378</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>46432</t>
+          <t>46663</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -4048,12 +4048,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>9,19%</t>
+          <t>9,0%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>17,14%</t>
+          <t>17,22%</t>
         </is>
       </c>
     </row>
@@ -4076,12 +4076,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>88698</t>
+          <t>88369</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>123436</t>
+          <t>122574</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -4091,12 +4091,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>32,73%</t>
+          <t>32,61%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>45,55%</t>
+          <t>45,24%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -4111,12 +4111,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>88698</t>
+          <t>88369</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>123436</t>
+          <t>122574</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -4126,12 +4126,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>32,73%</t>
+          <t>32,61%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>45,55%</t>
+          <t>45,24%</t>
         </is>
       </c>
     </row>
@@ -4154,12 +4154,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>78267</t>
+          <t>77955</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>111967</t>
+          <t>112174</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -4169,12 +4169,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>28,89%</t>
+          <t>28,77%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>41,32%</t>
+          <t>41,4%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -4189,12 +4189,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>78267</t>
+          <t>77955</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>111967</t>
+          <t>112174</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -4204,12 +4204,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>28,89%</t>
+          <t>28,77%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>41,32%</t>
+          <t>41,4%</t>
         </is>
       </c>
     </row>
@@ -4232,12 +4232,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>26415</t>
+          <t>25840</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>51168</t>
+          <t>51459</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -4247,12 +4247,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>9,75%</t>
+          <t>9,54%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>18,88%</t>
+          <t>18,99%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -4267,12 +4267,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>26415</t>
+          <t>25840</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>51168</t>
+          <t>51459</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -4282,12 +4282,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>9,75%</t>
+          <t>9,54%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>18,88%</t>
+          <t>18,99%</t>
         </is>
       </c>
     </row>
@@ -4392,12 +4392,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>22361</t>
+          <t>22325</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>43130</t>
+          <t>41608</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -4407,12 +4407,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>12,73%</t>
+          <t>12,71%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>24,56%</t>
+          <t>23,69%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -4427,12 +4427,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>22361</t>
+          <t>22325</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>43130</t>
+          <t>41608</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -4442,12 +4442,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>12,73%</t>
+          <t>12,71%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>24,56%</t>
+          <t>23,69%</t>
         </is>
       </c>
     </row>
@@ -4470,12 +4470,12 @@
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>50766</t>
+          <t>50253</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>76698</t>
+          <t>75637</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -4485,12 +4485,12 @@
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>28,9%</t>
+          <t>28,61%</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>43,67%</t>
+          <t>43,06%</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -4505,12 +4505,12 @@
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>50766</t>
+          <t>50253</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>76698</t>
+          <t>75637</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -4520,12 +4520,12 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>28,9%</t>
+          <t>28,61%</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>43,67%</t>
+          <t>43,06%</t>
         </is>
       </c>
     </row>
@@ -4548,12 +4548,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>36496</t>
+          <t>35946</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>60949</t>
+          <t>60777</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -4563,12 +4563,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>20,78%</t>
+          <t>20,47%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>34,7%</t>
+          <t>34,6%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -4583,12 +4583,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>36496</t>
+          <t>35946</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>60949</t>
+          <t>60777</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -4598,12 +4598,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>20,78%</t>
+          <t>20,47%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>34,7%</t>
+          <t>34,6%</t>
         </is>
       </c>
     </row>
@@ -4626,12 +4626,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>24825</t>
+          <t>24346</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>46234</t>
+          <t>45426</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -4641,12 +4641,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>14,13%</t>
+          <t>13,86%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>26,32%</t>
+          <t>25,86%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -4661,12 +4661,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>24825</t>
+          <t>24346</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>46234</t>
+          <t>45426</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -4676,12 +4676,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>14,13%</t>
+          <t>13,86%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>26,32%</t>
+          <t>25,86%</t>
         </is>
       </c>
     </row>
@@ -4786,12 +4786,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>73097</t>
+          <t>73109</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>110019</t>
+          <t>109969</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -4801,12 +4801,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>13,29%</t>
+          <t>13,3%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>20,01%</t>
+          <t>20,0%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -4821,12 +4821,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>73097</t>
+          <t>73109</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>110019</t>
+          <t>109969</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -4836,12 +4836,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>13,29%</t>
+          <t>13,3%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>20,01%</t>
+          <t>20,0%</t>
         </is>
       </c>
     </row>
@@ -4864,12 +4864,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>155241</t>
+          <t>156188</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>203419</t>
+          <t>202001</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -4879,12 +4879,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>28,24%</t>
+          <t>28,41%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>37,0%</t>
+          <t>36,74%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -4899,12 +4899,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>155241</t>
+          <t>156188</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>203419</t>
+          <t>202001</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -4914,12 +4914,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>28,24%</t>
+          <t>28,41%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>37,0%</t>
+          <t>36,74%</t>
         </is>
       </c>
     </row>
@@ -4942,12 +4942,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>141023</t>
+          <t>142418</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>188531</t>
+          <t>187163</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -4957,12 +4957,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>25,65%</t>
+          <t>25,9%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>34,29%</t>
+          <t>34,04%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -4977,12 +4977,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>141023</t>
+          <t>142418</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>188531</t>
+          <t>187163</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -4992,12 +4992,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>25,65%</t>
+          <t>25,9%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>34,29%</t>
+          <t>34,04%</t>
         </is>
       </c>
     </row>
@@ -5020,12 +5020,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>98364</t>
+          <t>99524</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>138685</t>
+          <t>140097</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -5035,12 +5035,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>17,89%</t>
+          <t>18,1%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>25,22%</t>
+          <t>25,48%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -5055,12 +5055,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>98364</t>
+          <t>99524</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>138685</t>
+          <t>140097</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -5070,12 +5070,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>17,89%</t>
+          <t>18,1%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>25,22%</t>
+          <t>25,48%</t>
         </is>
       </c>
     </row>
@@ -5180,12 +5180,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>95164</t>
+          <t>93836</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>132481</t>
+          <t>133591</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -5195,12 +5195,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>19,74%</t>
+          <t>19,46%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>27,48%</t>
+          <t>27,71%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -5215,12 +5215,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>95164</t>
+          <t>93836</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>132481</t>
+          <t>133591</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -5230,12 +5230,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>19,74%</t>
+          <t>19,46%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>27,48%</t>
+          <t>27,71%</t>
         </is>
       </c>
     </row>
@@ -5258,12 +5258,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>144673</t>
+          <t>144170</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>188998</t>
+          <t>188043</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -5273,12 +5273,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>30,0%</t>
+          <t>29,9%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>39,2%</t>
+          <t>39,0%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -5293,12 +5293,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>144673</t>
+          <t>144170</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>188998</t>
+          <t>188043</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -5308,12 +5308,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>30,0%</t>
+          <t>29,9%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>39,2%</t>
+          <t>39,0%</t>
         </is>
       </c>
     </row>
@@ -5336,12 +5336,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>94704</t>
+          <t>94471</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>133698</t>
+          <t>134532</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -5351,12 +5351,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>19,64%</t>
+          <t>19,59%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>27,73%</t>
+          <t>27,9%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -5371,12 +5371,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>94704</t>
+          <t>94471</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>133698</t>
+          <t>134532</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -5386,12 +5386,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>19,64%</t>
+          <t>19,59%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>27,73%</t>
+          <t>27,9%</t>
         </is>
       </c>
     </row>
@@ -5414,12 +5414,12 @@
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>73239</t>
+          <t>74329</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>110009</t>
+          <t>108504</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
@@ -5429,12 +5429,12 @@
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>15,19%</t>
+          <t>15,42%</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>22,82%</t>
+          <t>22,5%</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
@@ -5449,12 +5449,12 @@
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>73239</t>
+          <t>74329</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>110009</t>
+          <t>108504</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -5464,12 +5464,12 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>15,19%</t>
+          <t>15,42%</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
         <is>
-          <t>22,82%</t>
+          <t>22,5%</t>
         </is>
       </c>
     </row>
@@ -5554,7 +5554,7 @@
     <row r="29">
       <c r="A29" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>No ha trabajado</t>
         </is>
       </c>
       <c r="B29" s="3" t="inlineStr">
@@ -5574,12 +5574,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>128086</t>
+          <t>127697</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>171125</t>
+          <t>170384</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -5589,12 +5589,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>23,24%</t>
+          <t>23,17%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>31,05%</t>
+          <t>30,91%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -5609,12 +5609,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>128086</t>
+          <t>127697</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>171125</t>
+          <t>170384</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -5624,12 +5624,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>23,24%</t>
+          <t>23,17%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>31,05%</t>
+          <t>30,91%</t>
         </is>
       </c>
     </row>
@@ -5652,12 +5652,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>176020</t>
+          <t>177522</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>222127</t>
+          <t>221766</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -5667,12 +5667,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>31,93%</t>
+          <t>32,21%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>40,3%</t>
+          <t>40,23%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -5687,12 +5687,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>176020</t>
+          <t>177522</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>222127</t>
+          <t>221766</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -5702,12 +5702,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>31,93%</t>
+          <t>32,21%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>40,3%</t>
+          <t>40,23%</t>
         </is>
       </c>
     </row>
@@ -5730,12 +5730,12 @@
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>103541</t>
+          <t>102464</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>141936</t>
+          <t>143509</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -5745,12 +5745,12 @@
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>18,78%</t>
+          <t>18,59%</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>25,75%</t>
+          <t>26,04%</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
@@ -5765,12 +5765,12 @@
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>103541</t>
+          <t>102464</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>141936</t>
+          <t>143509</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
@@ -5780,12 +5780,12 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>18,78%</t>
+          <t>18,59%</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>25,75%</t>
+          <t>26,04%</t>
         </is>
       </c>
     </row>
@@ -5808,12 +5808,12 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>66473</t>
+          <t>65979</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>101162</t>
+          <t>100628</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -5823,12 +5823,12 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>12,06%</t>
+          <t>11,97%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>18,35%</t>
+          <t>18,26%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -5843,12 +5843,12 @@
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>66473</t>
+          <t>65979</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>101162</t>
+          <t>100628</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -5858,12 +5858,12 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>12,06%</t>
+          <t>11,97%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>18,35%</t>
+          <t>18,26%</t>
         </is>
       </c>
     </row>
@@ -5968,12 +5968,12 @@
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>407877</t>
+          <t>410292</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>491145</t>
+          <t>484438</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
@@ -5983,12 +5983,12 @@
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>17,84%</t>
+          <t>17,95%</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>21,49%</t>
+          <t>21,19%</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
@@ -6003,12 +6003,12 @@
       </c>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t>407877</t>
+          <t>410292</t>
         </is>
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>491145</t>
+          <t>484438</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
@@ -6018,12 +6018,12 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>17,84%</t>
+          <t>17,95%</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>21,49%</t>
+          <t>21,19%</t>
         </is>
       </c>
     </row>
@@ -6046,12 +6046,12 @@
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>740322</t>
+          <t>741245</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>834082</t>
+          <t>833927</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
@@ -6061,12 +6061,12 @@
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>32,39%</t>
+          <t>32,43%</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>36,49%</t>
+          <t>36,48%</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
@@ -6081,12 +6081,12 @@
       </c>
       <c r="L35" s="2" t="inlineStr">
         <is>
-          <t>740322</t>
+          <t>741245</t>
         </is>
       </c>
       <c r="M35" s="2" t="inlineStr">
         <is>
-          <t>834082</t>
+          <t>833927</t>
         </is>
       </c>
       <c r="N35" s="2" t="inlineStr">
@@ -6096,12 +6096,12 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>32,39%</t>
+          <t>32,43%</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
         <is>
-          <t>36,49%</t>
+          <t>36,48%</t>
         </is>
       </c>
     </row>
@@ -6124,12 +6124,12 @@
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>592982</t>
+          <t>589836</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>683990</t>
+          <t>682917</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
@@ -6139,12 +6139,12 @@
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>25,94%</t>
+          <t>25,81%</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>29,92%</t>
+          <t>29,88%</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr">
@@ -6159,12 +6159,12 @@
       </c>
       <c r="L36" s="2" t="inlineStr">
         <is>
-          <t>592982</t>
+          <t>589836</t>
         </is>
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>683990</t>
+          <t>682917</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
@@ -6174,12 +6174,12 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>25,94%</t>
+          <t>25,81%</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t>29,92%</t>
+          <t>29,88%</t>
         </is>
       </c>
     </row>
@@ -6202,12 +6202,12 @@
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>377923</t>
+          <t>377171</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>454730</t>
+          <t>456200</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
@@ -6217,12 +6217,12 @@
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>16,53%</t>
+          <t>16,5%</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>19,89%</t>
+          <t>19,96%</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
@@ -6237,12 +6237,12 @@
       </c>
       <c r="L37" s="2" t="inlineStr">
         <is>
-          <t>377923</t>
+          <t>377171</t>
         </is>
       </c>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t>454730</t>
+          <t>456200</t>
         </is>
       </c>
       <c r="N37" s="2" t="inlineStr">
@@ -6252,12 +6252,12 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>16,53%</t>
+          <t>16,5%</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
         <is>
-          <t>19,89%</t>
+          <t>19,96%</t>
         </is>
       </c>
     </row>
@@ -6535,12 +6535,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>25160</t>
+          <t>25886</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>50432</t>
+          <t>47725</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -6550,12 +6550,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>9,28%</t>
+          <t>9,55%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>18,6%</t>
+          <t>17,6%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -6570,12 +6570,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>25160</t>
+          <t>25886</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>50432</t>
+          <t>47725</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -6585,12 +6585,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>9,28%</t>
+          <t>9,55%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>18,6%</t>
+          <t>17,6%</t>
         </is>
       </c>
     </row>
@@ -6613,12 +6613,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>95932</t>
+          <t>96426</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>130514</t>
+          <t>129366</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -6628,12 +6628,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>35,38%</t>
+          <t>35,56%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>48,13%</t>
+          <t>47,71%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -6648,12 +6648,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>95932</t>
+          <t>96426</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>130514</t>
+          <t>129366</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -6663,12 +6663,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>35,38%</t>
+          <t>35,56%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>48,13%</t>
+          <t>47,71%</t>
         </is>
       </c>
     </row>
@@ -6691,12 +6691,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>67056</t>
+          <t>68170</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>97486</t>
+          <t>98296</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -6706,12 +6706,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>24,73%</t>
+          <t>25,14%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>35,95%</t>
+          <t>36,25%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -6726,12 +6726,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>67056</t>
+          <t>68170</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>97486</t>
+          <t>98296</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -6741,12 +6741,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>24,73%</t>
+          <t>25,14%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>35,95%</t>
+          <t>36,25%</t>
         </is>
       </c>
     </row>
@@ -6769,12 +6769,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>30275</t>
+          <t>30137</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>53490</t>
+          <t>54779</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -6784,12 +6784,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>11,16%</t>
+          <t>11,11%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>19,73%</t>
+          <t>20,2%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -6804,12 +6804,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>30275</t>
+          <t>30137</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>53490</t>
+          <t>54779</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -6819,12 +6819,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>11,16%</t>
+          <t>11,11%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>19,73%</t>
+          <t>20,2%</t>
         </is>
       </c>
     </row>
@@ -6929,12 +6929,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>29515</t>
+          <t>30045</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>54637</t>
+          <t>54635</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -6944,12 +6944,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>9,82%</t>
+          <t>10,0%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>18,19%</t>
+          <t>18,18%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -6964,12 +6964,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>29515</t>
+          <t>30045</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>54637</t>
+          <t>54635</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -6979,12 +6979,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>9,82%</t>
+          <t>10,0%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>18,19%</t>
+          <t>18,18%</t>
         </is>
       </c>
     </row>
@@ -7007,12 +7007,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>118531</t>
+          <t>119919</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>154725</t>
+          <t>155204</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -7022,12 +7022,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>39,45%</t>
+          <t>39,91%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>51,5%</t>
+          <t>51,66%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -7042,12 +7042,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>118531</t>
+          <t>119919</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>154725</t>
+          <t>155204</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -7057,12 +7057,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>39,45%</t>
+          <t>39,91%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>51,5%</t>
+          <t>51,66%</t>
         </is>
       </c>
     </row>
@@ -7085,12 +7085,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>65832</t>
+          <t>64549</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>96720</t>
+          <t>94666</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -7100,12 +7100,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>21,91%</t>
+          <t>21,48%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>32,19%</t>
+          <t>31,51%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -7120,12 +7120,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>65832</t>
+          <t>64549</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>96720</t>
+          <t>94666</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -7135,12 +7135,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>21,91%</t>
+          <t>21,48%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>32,19%</t>
+          <t>31,51%</t>
         </is>
       </c>
     </row>
@@ -7163,12 +7163,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>32585</t>
+          <t>33198</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>60162</t>
+          <t>58750</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -7178,12 +7178,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>10,85%</t>
+          <t>11,05%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>20,02%</t>
+          <t>19,55%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -7198,12 +7198,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>32585</t>
+          <t>33198</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>60162</t>
+          <t>58750</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -7213,12 +7213,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>10,85%</t>
+          <t>11,05%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>20,02%</t>
+          <t>19,55%</t>
         </is>
       </c>
     </row>
@@ -7323,12 +7323,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>19255</t>
+          <t>19689</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>38825</t>
+          <t>39078</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -7338,12 +7338,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>16,07%</t>
+          <t>16,43%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>32,41%</t>
+          <t>32,62%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -7358,12 +7358,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>19255</t>
+          <t>19689</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>38825</t>
+          <t>39078</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -7373,12 +7373,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>16,07%</t>
+          <t>16,43%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>32,41%</t>
+          <t>32,62%</t>
         </is>
       </c>
     </row>
@@ -7401,12 +7401,12 @@
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>39441</t>
+          <t>38703</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>61629</t>
+          <t>60869</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -7416,12 +7416,12 @@
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>32,92%</t>
+          <t>32,3%</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>51,44%</t>
+          <t>50,81%</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -7436,12 +7436,12 @@
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>39441</t>
+          <t>38703</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>61629</t>
+          <t>60869</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -7451,12 +7451,12 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>32,92%</t>
+          <t>32,3%</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>51,44%</t>
+          <t>50,81%</t>
         </is>
       </c>
     </row>
@@ -7479,12 +7479,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>19598</t>
+          <t>19529</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>39415</t>
+          <t>39606</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -7494,12 +7494,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>16,36%</t>
+          <t>16,3%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>32,9%</t>
+          <t>33,06%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -7514,12 +7514,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>19598</t>
+          <t>19529</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>39415</t>
+          <t>39606</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -7529,12 +7529,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>16,36%</t>
+          <t>16,3%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>32,9%</t>
+          <t>33,06%</t>
         </is>
       </c>
     </row>
@@ -7557,12 +7557,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>7321</t>
+          <t>6870</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>20717</t>
+          <t>20393</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -7572,12 +7572,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>6,11%</t>
+          <t>5,73%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>17,29%</t>
+          <t>17,02%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -7592,12 +7592,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>7321</t>
+          <t>6870</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>20717</t>
+          <t>20393</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -7607,12 +7607,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>6,11%</t>
+          <t>5,73%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>17,29%</t>
+          <t>17,02%</t>
         </is>
       </c>
     </row>
@@ -7717,12 +7717,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>86707</t>
+          <t>87465</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>124675</t>
+          <t>124856</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -7732,12 +7732,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>15,12%</t>
+          <t>15,25%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>21,74%</t>
+          <t>21,77%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -7752,12 +7752,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>86707</t>
+          <t>87465</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>124675</t>
+          <t>124856</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -7767,12 +7767,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>15,12%</t>
+          <t>15,25%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>21,74%</t>
+          <t>21,77%</t>
         </is>
       </c>
     </row>
@@ -7795,12 +7795,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>226202</t>
+          <t>225924</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>276855</t>
+          <t>276500</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -7810,12 +7810,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>39,44%</t>
+          <t>39,4%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>48,28%</t>
+          <t>48,22%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -7830,12 +7830,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>226202</t>
+          <t>225924</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>276855</t>
+          <t>276500</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -7845,12 +7845,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>39,44%</t>
+          <t>39,4%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>48,28%</t>
+          <t>48,22%</t>
         </is>
       </c>
     </row>
@@ -7873,12 +7873,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>114179</t>
+          <t>112837</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>154851</t>
+          <t>153354</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -7888,12 +7888,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>19,91%</t>
+          <t>19,68%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>27,0%</t>
+          <t>26,74%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -7908,12 +7908,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>114179</t>
+          <t>112837</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>154851</t>
+          <t>153354</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -7923,12 +7923,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>19,91%</t>
+          <t>19,68%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>27,0%</t>
+          <t>26,74%</t>
         </is>
       </c>
     </row>
@@ -7951,12 +7951,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>70043</t>
+          <t>69408</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>104868</t>
+          <t>104406</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -7966,12 +7966,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>12,21%</t>
+          <t>12,1%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>18,29%</t>
+          <t>18,21%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -7986,12 +7986,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>70043</t>
+          <t>69408</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>104868</t>
+          <t>104406</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -8001,12 +8001,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>12,21%</t>
+          <t>12,1%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>18,29%</t>
+          <t>18,21%</t>
         </is>
       </c>
     </row>
@@ -8111,12 +8111,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>121935</t>
+          <t>119723</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>164905</t>
+          <t>160467</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -8126,12 +8126,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>26,98%</t>
+          <t>26,49%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>36,48%</t>
+          <t>35,5%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -8146,12 +8146,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>121935</t>
+          <t>119723</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>164905</t>
+          <t>160467</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -8161,12 +8161,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>26,98%</t>
+          <t>26,49%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>36,48%</t>
+          <t>35,5%</t>
         </is>
       </c>
     </row>
@@ -8189,12 +8189,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>155914</t>
+          <t>157468</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>198938</t>
+          <t>199017</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -8204,12 +8204,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>34,5%</t>
+          <t>34,84%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>44,01%</t>
+          <t>44,03%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -8224,12 +8224,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>155914</t>
+          <t>157468</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>198938</t>
+          <t>199017</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -8239,12 +8239,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>34,5%</t>
+          <t>34,84%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>44,01%</t>
+          <t>44,03%</t>
         </is>
       </c>
     </row>
@@ -8267,12 +8267,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>65031</t>
+          <t>66224</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>98422</t>
+          <t>99764</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -8282,12 +8282,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>14,39%</t>
+          <t>14,65%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>21,78%</t>
+          <t>22,07%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -8302,12 +8302,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>65031</t>
+          <t>66224</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>98422</t>
+          <t>99764</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -8317,12 +8317,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>14,39%</t>
+          <t>14,65%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>21,78%</t>
+          <t>22,07%</t>
         </is>
       </c>
     </row>
@@ -8345,12 +8345,12 @@
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>38908</t>
+          <t>38513</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>65963</t>
+          <t>66649</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
@@ -8360,12 +8360,12 @@
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>8,61%</t>
+          <t>8,52%</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>14,59%</t>
+          <t>14,75%</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
@@ -8380,12 +8380,12 @@
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>38908</t>
+          <t>38513</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>65963</t>
+          <t>66649</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -8395,12 +8395,12 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>8,61%</t>
+          <t>8,52%</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
         <is>
-          <t>14,59%</t>
+          <t>14,75%</t>
         </is>
       </c>
     </row>
@@ -8485,7 +8485,7 @@
     <row r="29">
       <c r="A29" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>No ha trabajado</t>
         </is>
       </c>
       <c r="B29" s="3" t="inlineStr">
@@ -8505,12 +8505,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>155033</t>
+          <t>154930</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>197473</t>
+          <t>198714</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -8520,12 +8520,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>30,19%</t>
+          <t>30,17%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>38,45%</t>
+          <t>38,69%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -8540,12 +8540,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>155033</t>
+          <t>154930</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>197473</t>
+          <t>198714</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -8555,12 +8555,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>30,19%</t>
+          <t>30,17%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>38,45%</t>
+          <t>38,69%</t>
         </is>
       </c>
     </row>
@@ -8583,12 +8583,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>181481</t>
+          <t>180074</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>225202</t>
+          <t>224579</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -8598,12 +8598,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>35,34%</t>
+          <t>35,06%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>43,85%</t>
+          <t>43,73%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -8618,12 +8618,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>181481</t>
+          <t>180074</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>225202</t>
+          <t>224579</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -8633,12 +8633,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>35,34%</t>
+          <t>35,06%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>43,85%</t>
+          <t>43,73%</t>
         </is>
       </c>
     </row>
@@ -8661,12 +8661,12 @@
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>73197</t>
+          <t>72676</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>109024</t>
+          <t>107685</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -8676,12 +8676,12 @@
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>14,25%</t>
+          <t>14,15%</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>21,23%</t>
+          <t>20,97%</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
@@ -8696,12 +8696,12 @@
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>73197</t>
+          <t>72676</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>109024</t>
+          <t>107685</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
@@ -8711,12 +8711,12 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>14,25%</t>
+          <t>14,15%</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>21,23%</t>
+          <t>20,97%</t>
         </is>
       </c>
     </row>
@@ -8739,12 +8739,12 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>34169</t>
+          <t>34392</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>61894</t>
+          <t>63190</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -8754,12 +8754,12 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>6,65%</t>
+          <t>6,7%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>12,05%</t>
+          <t>12,3%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -8774,12 +8774,12 @@
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>34169</t>
+          <t>34392</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>61894</t>
+          <t>63190</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -8789,12 +8789,12 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>6,65%</t>
+          <t>6,7%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>12,05%</t>
+          <t>12,3%</t>
         </is>
       </c>
     </row>
@@ -8899,12 +8899,12 @@
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>488374</t>
+          <t>488818</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>569074</t>
+          <t>574915</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
@@ -8914,12 +8914,12 @@
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>21,9%</t>
+          <t>21,92%</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>25,51%</t>
+          <t>25,78%</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
@@ -8934,12 +8934,12 @@
       </c>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t>488374</t>
+          <t>488818</t>
         </is>
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>569074</t>
+          <t>574915</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
@@ -8949,12 +8949,12 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>21,9%</t>
+          <t>21,92%</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>25,51%</t>
+          <t>25,78%</t>
         </is>
       </c>
     </row>
@@ -8977,12 +8977,12 @@
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>880616</t>
+          <t>883456</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>979169</t>
+          <t>972987</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
@@ -8992,12 +8992,12 @@
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>39,48%</t>
+          <t>39,61%</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>43,9%</t>
+          <t>43,62%</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
@@ -9012,12 +9012,12 @@
       </c>
       <c r="L35" s="2" t="inlineStr">
         <is>
-          <t>880616</t>
+          <t>883456</t>
         </is>
       </c>
       <c r="M35" s="2" t="inlineStr">
         <is>
-          <t>979169</t>
+          <t>972987</t>
         </is>
       </c>
       <c r="N35" s="2" t="inlineStr">
@@ -9027,12 +9027,12 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>39,48%</t>
+          <t>39,61%</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
         <is>
-          <t>43,9%</t>
+          <t>43,62%</t>
         </is>
       </c>
     </row>
@@ -9055,12 +9055,12 @@
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>455077</t>
+          <t>452273</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>534905</t>
+          <t>531375</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
@@ -9070,12 +9070,12 @@
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>20,4%</t>
+          <t>20,28%</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>23,98%</t>
+          <t>23,82%</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr">
@@ -9090,12 +9090,12 @@
       </c>
       <c r="L36" s="2" t="inlineStr">
         <is>
-          <t>455077</t>
+          <t>452273</t>
         </is>
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>534905</t>
+          <t>531375</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
@@ -9105,12 +9105,12 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>20,4%</t>
+          <t>20,28%</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t>23,98%</t>
+          <t>23,82%</t>
         </is>
       </c>
     </row>
@@ -9133,12 +9133,12 @@
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>250131</t>
+          <t>254237</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>313481</t>
+          <t>317015</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
@@ -9148,12 +9148,12 @@
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>11,21%</t>
+          <t>11,4%</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>14,05%</t>
+          <t>14,21%</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
@@ -9168,12 +9168,12 @@
       </c>
       <c r="L37" s="2" t="inlineStr">
         <is>
-          <t>250131</t>
+          <t>254237</t>
         </is>
       </c>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t>313481</t>
+          <t>317015</t>
         </is>
       </c>
       <c r="N37" s="2" t="inlineStr">
@@ -9183,12 +9183,12 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>11,21%</t>
+          <t>11,4%</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
         <is>
-          <t>14,05%</t>
+          <t>14,21%</t>
         </is>
       </c>
     </row>
@@ -9461,32 +9461,32 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>42889</t>
+          <t>45288</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>34858</t>
+          <t>36085</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>52704</t>
+          <t>55416</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>18,63%</t>
+          <t>18,13%</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>15,14%</t>
+          <t>14,44%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>22,89%</t>
+          <t>22,18%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -9496,32 +9496,32 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>42889</t>
+          <t>45288</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>34858</t>
+          <t>36085</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>52704</t>
+          <t>55416</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>18,63%</t>
+          <t>18,13%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>15,14%</t>
+          <t>14,44%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>22,89%</t>
+          <t>22,18%</t>
         </is>
       </c>
     </row>
@@ -9539,32 +9539,32 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>82441</t>
+          <t>87949</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>70233</t>
+          <t>76245</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>95063</t>
+          <t>100587</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>35,81%</t>
+          <t>35,2%</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>30,5%</t>
+          <t>30,52%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>41,29%</t>
+          <t>40,26%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -9574,32 +9574,32 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>82441</t>
+          <t>87949</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>70233</t>
+          <t>76245</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>95063</t>
+          <t>100587</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>35,81%</t>
+          <t>35,2%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>30,5%</t>
+          <t>30,52%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>41,29%</t>
+          <t>40,26%</t>
         </is>
       </c>
     </row>
@@ -9617,32 +9617,32 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>60434</t>
+          <t>68498</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>50333</t>
+          <t>57378</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>72040</t>
+          <t>81027</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>26,25%</t>
+          <t>27,42%</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>21,86%</t>
+          <t>22,97%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>31,29%</t>
+          <t>32,43%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -9652,32 +9652,32 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>60434</t>
+          <t>68498</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>50333</t>
+          <t>57378</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>72040</t>
+          <t>81027</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>26,25%</t>
+          <t>27,42%</t>
         </is>
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>21,86%</t>
+          <t>22,97%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>31,29%</t>
+          <t>32,43%</t>
         </is>
       </c>
     </row>
@@ -9695,32 +9695,32 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>44473</t>
+          <t>48105</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>34990</t>
+          <t>37874</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>55275</t>
+          <t>60587</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>19,32%</t>
+          <t>19,25%</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>15,2%</t>
+          <t>15,16%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>24,01%</t>
+          <t>24,25%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -9730,32 +9730,32 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>44473</t>
+          <t>48105</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>34990</t>
+          <t>37874</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>55275</t>
+          <t>60587</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>19,32%</t>
+          <t>19,25%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>15,2%</t>
+          <t>15,16%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>24,01%</t>
+          <t>24,25%</t>
         </is>
       </c>
     </row>
@@ -9773,17 +9773,17 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>230236</t>
+          <t>249840</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>230236</t>
+          <t>249840</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>230236</t>
+          <t>249840</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -9808,17 +9808,17 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>230236</t>
+          <t>249840</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>230236</t>
+          <t>249840</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>230236</t>
+          <t>249840</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -9855,32 +9855,32 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>36748</t>
+          <t>42410</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>28226</t>
+          <t>33455</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>45719</t>
+          <t>53117</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>17,7%</t>
+          <t>18,43%</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>13,6%</t>
+          <t>14,54%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>22,02%</t>
+          <t>23,08%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -9890,32 +9890,32 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>36748</t>
+          <t>42410</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>28226</t>
+          <t>33455</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>45719</t>
+          <t>53117</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>17,7%</t>
+          <t>18,43%</t>
         </is>
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>13,6%</t>
+          <t>14,54%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>22,02%</t>
+          <t>23,08%</t>
         </is>
       </c>
     </row>
@@ -9933,32 +9933,32 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>64972</t>
+          <t>72350</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>55195</t>
+          <t>61294</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>76350</t>
+          <t>86408</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>31,29%</t>
+          <t>31,44%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>26,58%</t>
+          <t>26,64%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>36,77%</t>
+          <t>37,55%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -9968,32 +9968,32 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>64972</t>
+          <t>72350</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>55195</t>
+          <t>61294</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>76350</t>
+          <t>86408</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>31,29%</t>
+          <t>31,44%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>26,58%</t>
+          <t>26,64%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>36,77%</t>
+          <t>37,55%</t>
         </is>
       </c>
     </row>
@@ -10011,32 +10011,32 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>67323</t>
+          <t>72510</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>55596</t>
+          <t>61007</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>79051</t>
+          <t>85734</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>32,43%</t>
+          <t>31,51%</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>26,78%</t>
+          <t>26,51%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>38,07%</t>
+          <t>37,26%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -10046,32 +10046,32 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>67323</t>
+          <t>72510</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>55596</t>
+          <t>61007</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>79051</t>
+          <t>85734</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>32,43%</t>
+          <t>31,51%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>26,78%</t>
+          <t>26,51%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>38,07%</t>
+          <t>37,26%</t>
         </is>
       </c>
     </row>
@@ -10089,32 +10089,32 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>38578</t>
+          <t>42841</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>28632</t>
+          <t>32580</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>48707</t>
+          <t>53611</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>18,58%</t>
+          <t>18,62%</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>13,79%</t>
+          <t>14,16%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>23,46%</t>
+          <t>23,3%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -10124,32 +10124,32 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>38578</t>
+          <t>42841</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>28632</t>
+          <t>32580</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>48707</t>
+          <t>53611</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>18,58%</t>
+          <t>18,62%</t>
         </is>
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>13,79%</t>
+          <t>14,16%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>23,46%</t>
+          <t>23,3%</t>
         </is>
       </c>
     </row>
@@ -10167,17 +10167,17 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>207621</t>
+          <t>230111</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>207621</t>
+          <t>230111</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>207621</t>
+          <t>230111</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -10202,17 +10202,17 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>207621</t>
+          <t>230111</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>207621</t>
+          <t>230111</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>207621</t>
+          <t>230111</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -10249,32 +10249,32 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>22988</t>
+          <t>24001</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>17780</t>
+          <t>17778</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>29766</t>
+          <t>30949</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>31,27%</t>
+          <t>29,48%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>24,19%</t>
+          <t>21,84%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>40,49%</t>
+          <t>38,02%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -10284,32 +10284,32 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>22988</t>
+          <t>24001</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>17780</t>
+          <t>17778</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>29766</t>
+          <t>30949</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>31,27%</t>
+          <t>29,48%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>24,19%</t>
+          <t>21,84%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>40,49%</t>
+          <t>38,02%</t>
         </is>
       </c>
     </row>
@@ -10327,32 +10327,32 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>25553</t>
+          <t>28824</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>19950</t>
+          <t>22256</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>32898</t>
+          <t>36274</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>34,76%</t>
+          <t>35,41%</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>27,14%</t>
+          <t>27,34%</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>44,76%</t>
+          <t>44,56%</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -10362,32 +10362,32 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>25553</t>
+          <t>28824</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>19950</t>
+          <t>22256</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>32898</t>
+          <t>36274</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>34,76%</t>
+          <t>35,41%</t>
         </is>
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>27,14%</t>
+          <t>27,34%</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>44,76%</t>
+          <t>44,56%</t>
         </is>
       </c>
     </row>
@@ -10405,32 +10405,32 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>15685</t>
+          <t>17595</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>10622</t>
+          <t>11886</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>21589</t>
+          <t>23522</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>21,34%</t>
+          <t>21,61%</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>14,45%</t>
+          <t>14,6%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>29,37%</t>
+          <t>28,9%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -10440,32 +10440,32 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>15685</t>
+          <t>17595</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>10622</t>
+          <t>11886</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>21589</t>
+          <t>23522</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>21,34%</t>
+          <t>21,61%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>14,45%</t>
+          <t>14,6%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>29,37%</t>
+          <t>28,9%</t>
         </is>
       </c>
     </row>
@@ -10483,32 +10483,32 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>9282</t>
+          <t>10985</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>5330</t>
+          <t>6213</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>14545</t>
+          <t>16980</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>12,63%</t>
+          <t>13,49%</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>7,25%</t>
+          <t>7,63%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>19,79%</t>
+          <t>20,86%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -10518,32 +10518,32 @@
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>9282</t>
+          <t>10985</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>5330</t>
+          <t>6213</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>14545</t>
+          <t>16980</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>12,63%</t>
+          <t>13,49%</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>7,25%</t>
+          <t>7,63%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>19,79%</t>
+          <t>20,86%</t>
         </is>
       </c>
     </row>
@@ -10561,17 +10561,17 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>73507</t>
+          <t>81404</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>73507</t>
+          <t>81404</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>73507</t>
+          <t>81404</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -10596,17 +10596,17 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>73507</t>
+          <t>81404</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>73507</t>
+          <t>81404</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>73507</t>
+          <t>81404</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -10643,32 +10643,32 @@
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>90220</t>
+          <t>99709</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>77063</t>
+          <t>85587</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>103391</t>
+          <t>114173</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>25,29%</t>
+          <t>25,18%</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>21,61%</t>
+          <t>21,62%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>28,99%</t>
+          <t>28,83%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -10678,32 +10678,32 @@
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>90220</t>
+          <t>99709</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>77063</t>
+          <t>85587</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>103391</t>
+          <t>114173</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>25,29%</t>
+          <t>25,18%</t>
         </is>
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>21,61%</t>
+          <t>21,62%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>28,99%</t>
+          <t>28,83%</t>
         </is>
       </c>
     </row>
@@ -10721,32 +10721,32 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>136639</t>
+          <t>152332</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>120564</t>
+          <t>134798</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>152548</t>
+          <t>169245</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>38,31%</t>
+          <t>38,47%</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>33,8%</t>
+          <t>34,04%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>42,77%</t>
+          <t>42,74%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -10756,32 +10756,32 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>136639</t>
+          <t>152332</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>120564</t>
+          <t>134798</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>152548</t>
+          <t>169245</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>38,31%</t>
+          <t>38,47%</t>
         </is>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>33,8%</t>
+          <t>34,04%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>42,77%</t>
+          <t>42,74%</t>
         </is>
       </c>
     </row>
@@ -10799,32 +10799,32 @@
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>75562</t>
+          <t>82915</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>63802</t>
+          <t>70293</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>90109</t>
+          <t>98309</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>21,19%</t>
+          <t>20,94%</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>17,89%</t>
+          <t>17,75%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>25,26%</t>
+          <t>24,83%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -10834,32 +10834,32 @@
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>75562</t>
+          <t>82915</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>63802</t>
+          <t>70293</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>90109</t>
+          <t>98309</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>21,19%</t>
+          <t>20,94%</t>
         </is>
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>17,89%</t>
+          <t>17,75%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>25,26%</t>
+          <t>24,83%</t>
         </is>
       </c>
     </row>
@@ -10877,32 +10877,32 @@
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>54250</t>
+          <t>61001</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>43316</t>
+          <t>48958</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>68511</t>
+          <t>74190</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>15,21%</t>
+          <t>15,41%</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>12,14%</t>
+          <t>12,36%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>19,21%</t>
+          <t>18,74%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -10912,32 +10912,32 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>54250</t>
+          <t>61001</t>
         </is>
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>43316</t>
+          <t>48958</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>68511</t>
+          <t>74190</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
         <is>
-          <t>15,21%</t>
+          <t>15,41%</t>
         </is>
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>12,14%</t>
+          <t>12,36%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>19,21%</t>
+          <t>18,74%</t>
         </is>
       </c>
     </row>
@@ -10955,17 +10955,17 @@
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>356671</t>
+          <t>395957</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>356671</t>
+          <t>395957</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>356671</t>
+          <t>395957</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -10990,17 +10990,17 @@
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>356671</t>
+          <t>395957</t>
         </is>
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>356671</t>
+          <t>395957</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>356671</t>
+          <t>395957</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -11037,32 +11037,32 @@
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>205854</t>
+          <t>114324</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>140872</t>
+          <t>100201</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>293251</t>
+          <t>127706</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>51,21%</t>
+          <t>35,22%</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>35,04%</t>
+          <t>30,87%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>72,95%</t>
+          <t>39,34%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -11072,32 +11072,32 @@
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>205854</t>
+          <t>114324</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>140872</t>
+          <t>100201</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>293251</t>
+          <t>127706</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>51,21%</t>
+          <t>35,22%</t>
         </is>
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>35,04%</t>
+          <t>30,87%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>72,95%</t>
+          <t>39,34%</t>
         </is>
       </c>
     </row>
@@ -11115,32 +11115,32 @@
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>109709</t>
+          <t>116051</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>58755</t>
+          <t>103066</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>144953</t>
+          <t>130640</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>27,29%</t>
+          <t>35,75%</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>14,62%</t>
+          <t>31,75%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>36,06%</t>
+          <t>40,24%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -11150,32 +11150,32 @@
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>109709</t>
+          <t>116051</t>
         </is>
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>58755</t>
+          <t>103066</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>144953</t>
+          <t>130640</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
         <is>
-          <t>27,29%</t>
+          <t>35,75%</t>
         </is>
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>14,62%</t>
+          <t>31,75%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>36,06%</t>
+          <t>40,24%</t>
         </is>
       </c>
     </row>
@@ -11193,32 +11193,32 @@
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>54623</t>
+          <t>59190</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>32040</t>
+          <t>48086</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>76423</t>
+          <t>69942</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
         <is>
-          <t>13,59%</t>
+          <t>18,23%</t>
         </is>
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>7,97%</t>
+          <t>14,81%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>19,01%</t>
+          <t>21,55%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -11228,32 +11228,32 @@
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>54623</t>
+          <t>59190</t>
         </is>
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>32040</t>
+          <t>48086</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>76423</t>
+          <t>69942</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
         <is>
-          <t>13,59%</t>
+          <t>18,23%</t>
         </is>
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>7,97%</t>
+          <t>14,81%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>19,01%</t>
+          <t>21,55%</t>
         </is>
       </c>
     </row>
@@ -11271,32 +11271,32 @@
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>31812</t>
+          <t>35050</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>17422</t>
+          <t>26962</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>45006</t>
+          <t>45118</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>7,91%</t>
+          <t>10,8%</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>4,33%</t>
+          <t>8,31%</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>11,2%</t>
+          <t>13,9%</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
@@ -11306,32 +11306,32 @@
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>31812</t>
+          <t>35050</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>17422</t>
+          <t>26962</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>45006</t>
+          <t>45118</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
         <is>
-          <t>7,91%</t>
+          <t>10,8%</t>
         </is>
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>4,33%</t>
+          <t>8,31%</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
         <is>
-          <t>11,2%</t>
+          <t>13,9%</t>
         </is>
       </c>
     </row>
@@ -11349,17 +11349,17 @@
       </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
-          <t>401999</t>
+          <t>324615</t>
         </is>
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>401999</t>
+          <t>324615</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>401999</t>
+          <t>324615</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -11384,17 +11384,17 @@
       </c>
       <c r="K28" s="2" t="inlineStr">
         <is>
-          <t>401999</t>
+          <t>324615</t>
         </is>
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>401999</t>
+          <t>324615</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>401999</t>
+          <t>324615</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -11416,7 +11416,7 @@
     <row r="29">
       <c r="A29" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>No ha trabajado</t>
         </is>
       </c>
       <c r="B29" s="3" t="inlineStr">
@@ -11431,32 +11431,32 @@
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>129734</t>
+          <t>140414</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>115605</t>
+          <t>126461</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>143444</t>
+          <t>153415</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>49,58%</t>
+          <t>49,55%</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>44,18%</t>
+          <t>44,63%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>54,82%</t>
+          <t>54,14%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -11466,32 +11466,32 @@
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>129734</t>
+          <t>140414</t>
         </is>
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>115605</t>
+          <t>126461</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>143444</t>
+          <t>153415</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
         <is>
-          <t>49,58%</t>
+          <t>49,55%</t>
         </is>
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>44,18%</t>
+          <t>44,63%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>54,82%</t>
+          <t>54,14%</t>
         </is>
       </c>
     </row>
@@ -11509,32 +11509,32 @@
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>73328</t>
+          <t>80482</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>61179</t>
+          <t>69177</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>85234</t>
+          <t>95172</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>28,02%</t>
+          <t>28,4%</t>
         </is>
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>23,38%</t>
+          <t>24,41%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>32,57%</t>
+          <t>33,59%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -11544,32 +11544,32 @@
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>73328</t>
+          <t>80482</t>
         </is>
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>61179</t>
+          <t>69177</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>85234</t>
+          <t>95172</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
         <is>
-          <t>28,02%</t>
+          <t>28,4%</t>
         </is>
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>23,38%</t>
+          <t>24,41%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>32,57%</t>
+          <t>33,59%</t>
         </is>
       </c>
     </row>
@@ -11587,32 +11587,32 @@
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>38332</t>
+          <t>41948</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>29245</t>
+          <t>31963</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>50210</t>
+          <t>53651</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>14,65%</t>
+          <t>14,8%</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>11,18%</t>
+          <t>11,28%</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>19,19%</t>
+          <t>18,93%</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
@@ -11622,32 +11622,32 @@
       </c>
       <c r="K31" s="2" t="inlineStr">
         <is>
-          <t>38332</t>
+          <t>41948</t>
         </is>
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>29245</t>
+          <t>31963</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>50210</t>
+          <t>53651</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
         <is>
-          <t>14,65%</t>
+          <t>14,8%</t>
         </is>
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>11,18%</t>
+          <t>11,28%</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>19,19%</t>
+          <t>18,93%</t>
         </is>
       </c>
     </row>
@@ -11665,32 +11665,32 @@
       </c>
       <c r="D32" s="2" t="inlineStr">
         <is>
-          <t>20283</t>
+          <t>20506</t>
         </is>
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>13983</t>
+          <t>13969</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>28720</t>
+          <t>28916</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
         <is>
-          <t>7,75%</t>
+          <t>7,24%</t>
         </is>
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>5,34%</t>
+          <t>4,93%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>10,98%</t>
+          <t>10,2%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -11700,32 +11700,32 @@
       </c>
       <c r="K32" s="2" t="inlineStr">
         <is>
-          <t>20283</t>
+          <t>20506</t>
         </is>
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>13983</t>
+          <t>13969</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>28720</t>
+          <t>28916</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
         <is>
-          <t>7,75%</t>
+          <t>7,24%</t>
         </is>
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>5,34%</t>
+          <t>4,93%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>10,98%</t>
+          <t>10,2%</t>
         </is>
       </c>
     </row>
@@ -11743,17 +11743,17 @@
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>261677</t>
+          <t>283350</t>
         </is>
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>261677</t>
+          <t>283350</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>261677</t>
+          <t>283350</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
@@ -11778,17 +11778,17 @@
       </c>
       <c r="K33" s="2" t="inlineStr">
         <is>
-          <t>261677</t>
+          <t>283350</t>
         </is>
       </c>
       <c r="L33" s="2" t="inlineStr">
         <is>
-          <t>261677</t>
+          <t>283350</t>
         </is>
       </c>
       <c r="M33" s="2" t="inlineStr">
         <is>
-          <t>261677</t>
+          <t>283350</t>
         </is>
       </c>
       <c r="N33" s="2" t="inlineStr">
@@ -11825,32 +11825,32 @@
       </c>
       <c r="D34" s="2" t="inlineStr">
         <is>
-          <t>528433</t>
+          <t>466146</t>
         </is>
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>457363</t>
+          <t>439435</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>679920</t>
+          <t>501002</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
         <is>
-          <t>34,5%</t>
+          <t>29,78%</t>
         </is>
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>29,86%</t>
+          <t>28,07%</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>44,39%</t>
+          <t>32,01%</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
@@ -11860,32 +11860,32 @@
       </c>
       <c r="K34" s="2" t="inlineStr">
         <is>
-          <t>528433</t>
+          <t>466146</t>
         </is>
       </c>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t>457363</t>
+          <t>439435</t>
         </is>
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>679920</t>
+          <t>501002</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
         <is>
-          <t>34,5%</t>
+          <t>29,78%</t>
         </is>
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>29,86%</t>
+          <t>28,07%</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>44,39%</t>
+          <t>32,01%</t>
         </is>
       </c>
     </row>
@@ -11903,32 +11903,32 @@
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
-          <t>492642</t>
+          <t>537989</t>
         </is>
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>422539</t>
+          <t>508242</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>538116</t>
+          <t>571242</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
         <is>
-          <t>32,16%</t>
+          <t>34,37%</t>
         </is>
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>27,59%</t>
+          <t>32,47%</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>35,13%</t>
+          <t>36,49%</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
@@ -11938,32 +11938,32 @@
       </c>
       <c r="K35" s="2" t="inlineStr">
         <is>
-          <t>492642</t>
+          <t>537989</t>
         </is>
       </c>
       <c r="L35" s="2" t="inlineStr">
         <is>
-          <t>422539</t>
+          <t>508242</t>
         </is>
       </c>
       <c r="M35" s="2" t="inlineStr">
         <is>
-          <t>538116</t>
+          <t>571242</t>
         </is>
       </c>
       <c r="N35" s="2" t="inlineStr">
         <is>
-          <t>32,16%</t>
+          <t>34,37%</t>
         </is>
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>27,59%</t>
+          <t>32,47%</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
         <is>
-          <t>35,13%</t>
+          <t>36,49%</t>
         </is>
       </c>
     </row>
@@ -11981,32 +11981,32 @@
       </c>
       <c r="D36" s="2" t="inlineStr">
         <is>
-          <t>311959</t>
+          <t>342655</t>
         </is>
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>267206</t>
+          <t>314487</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>344848</t>
+          <t>370990</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
         <is>
-          <t>20,37%</t>
+          <t>21,89%</t>
         </is>
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>17,44%</t>
+          <t>20,09%</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>22,51%</t>
+          <t>23,7%</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr">
@@ -12016,32 +12016,32 @@
       </c>
       <c r="K36" s="2" t="inlineStr">
         <is>
-          <t>311959</t>
+          <t>342655</t>
         </is>
       </c>
       <c r="L36" s="2" t="inlineStr">
         <is>
-          <t>267206</t>
+          <t>314487</t>
         </is>
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>344848</t>
+          <t>370990</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
         <is>
-          <t>20,37%</t>
+          <t>21,89%</t>
         </is>
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>17,44%</t>
+          <t>20,09%</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t>22,51%</t>
+          <t>23,7%</t>
         </is>
       </c>
     </row>
@@ -12059,32 +12059,32 @@
       </c>
       <c r="D37" s="2" t="inlineStr">
         <is>
-          <t>198678</t>
+          <t>218488</t>
         </is>
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>164873</t>
+          <t>196769</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>223950</t>
+          <t>243150</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
         <is>
-          <t>12,97%</t>
+          <t>13,96%</t>
         </is>
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>10,76%</t>
+          <t>12,57%</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>14,62%</t>
+          <t>15,53%</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
@@ -12094,32 +12094,32 @@
       </c>
       <c r="K37" s="2" t="inlineStr">
         <is>
-          <t>198678</t>
+          <t>218488</t>
         </is>
       </c>
       <c r="L37" s="2" t="inlineStr">
         <is>
-          <t>164873</t>
+          <t>196769</t>
         </is>
       </c>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t>223950</t>
+          <t>243150</t>
         </is>
       </c>
       <c r="N37" s="2" t="inlineStr">
         <is>
-          <t>12,97%</t>
+          <t>13,96%</t>
         </is>
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>10,76%</t>
+          <t>12,57%</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
         <is>
-          <t>14,62%</t>
+          <t>15,53%</t>
         </is>
       </c>
     </row>
@@ -12137,17 +12137,17 @@
       </c>
       <c r="D38" s="2" t="inlineStr">
         <is>
-          <t>1531712</t>
+          <t>1565277</t>
         </is>
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>1531712</t>
+          <t>1565277</t>
         </is>
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
-          <t>1531712</t>
+          <t>1565277</t>
         </is>
       </c>
       <c r="G38" s="2" t="inlineStr">
@@ -12172,17 +12172,17 @@
       </c>
       <c r="K38" s="2" t="inlineStr">
         <is>
-          <t>1531712</t>
+          <t>1565277</t>
         </is>
       </c>
       <c r="L38" s="2" t="inlineStr">
         <is>
-          <t>1531712</t>
+          <t>1565277</t>
         </is>
       </c>
       <c r="M38" s="2" t="inlineStr">
         <is>
-          <t>1531712</t>
+          <t>1565277</t>
         </is>
       </c>
       <c r="N38" s="2" t="inlineStr">
